--- a/data/s1/Aradas/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s1/Aradas/archetypes/pop_archetypes_citizen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s1\Aradas\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19B3258-FAC8-4E98-BAB0-B5FEBA4B46C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1BEF6D-93C8-4E84-B2E3-F8176908639A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1097,7 +1097,6 @@
         <v>240</v>
       </c>
       <c r="Q5" s="8">
-        <f>1-0.0670582476749878</f>
         <v>0.9329417523250122</v>
       </c>
       <c r="R5" s="11">
@@ -1279,9 +1278,6 @@
       <c r="AL6" s="7">
         <v>99999</v>
       </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="Q10" s="3"/>
@@ -1336,7 +1332,6 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="Q16" s="3"/>
       <c r="S16" s="1"/>
     </row>
   </sheetData>
